--- a/reports/classification-round2-20261025T120026Z/human_review_250_final.xlsx
+++ b/reports/classification-round2-20261025T120026Z/human_review_250_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\All pro\Wadi project\Wadi Visit\reports\classification-round2-20261025T120026Z\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE1BC63A-C970-4059-BA15-E5ACAA0A83A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB4ED4AB-33A8-49D2-96C1-0E5943F26221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2685,9 +2685,6 @@
     <t>أول نقلة ستطلب مستقبلًا؛ الاعتماد على المنتج لا يثبت التحميل.</t>
   </si>
   <si>
-    <t>النص يذكر تجربة أولى ناجحة لهايدا ثم عرض البريمو؛ جهة التجربة ملتبسة ولا تثبت أول تعامل بالوادي.</t>
-  </si>
-  <si>
     <t>اتفاق على أول طلبية غدًا أو بعد غد، لا تحميل مثبت.</t>
   </si>
   <si>
@@ -2985,18 +2982,12 @@
     <t>تفاوض على التمويل وطلب جلسة ثانية بحضور شريكه.</t>
   </si>
   <si>
-    <t>تعامل متوقف مع وعد بالرجوع؛ فرصة إعادة تشغيل دون تنفيذ.</t>
-  </si>
-  <si>
     <t>عميل سابق يتفاوض على رجوعه وعمولة الوكيل.</t>
   </si>
   <si>
     <t>عميل وادي قائم من ماجد نجاح؛ الاتفاق يتعلق بطلب إضافي.</t>
   </si>
   <si>
-    <t>تعامل وادي سابق ومناقشة تركيز على عنابر قديمة؛ رجوع العميل نفسه غير مؤكد.</t>
-  </si>
-  <si>
     <t>مرتبط بموزع يرفض الكاش؛ لا مسار مقبول لبدء التعامل مذكور.</t>
   </si>
   <si>
@@ -3412,6 +3403,15 @@
   </si>
   <si>
     <t>شغال الوادي من شركة أسيوط ونزل حمولة بالفعل.</t>
+  </si>
+  <si>
+    <t>التجربة تخص هايدا؛ عرض البريمو ومتابعته فرصة للوادي، وليست أول تعامل</t>
+  </si>
+  <si>
+    <t>التعامل متوقف، والعودة رغبة من المندوب دون موافقة العميل</t>
+  </si>
+  <si>
+    <t>وافق على العودة للعمل، ولم يبدأ التنفيذ</t>
   </si>
 </sst>
 </file>
@@ -4071,10 +4071,10 @@
         <v>47</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>883</v>
+        <v>1123</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>14</v>
@@ -4112,7 +4112,7 @@
         <v>26</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>14</v>
@@ -4150,7 +4150,7 @@
         <v>86</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>56</v>
@@ -4188,7 +4188,7 @@
         <v>26</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>56</v>
@@ -4226,7 +4226,7 @@
         <v>15</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>56</v>
@@ -4264,7 +4264,7 @@
         <v>15</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>56</v>
@@ -4302,7 +4302,7 @@
         <v>26</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>56</v>
@@ -4340,7 +4340,7 @@
         <v>26</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>56</v>
@@ -4378,7 +4378,7 @@
         <v>16</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>56</v>
@@ -4416,7 +4416,7 @@
         <v>26</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>56</v>
@@ -4454,7 +4454,7 @@
         <v>15</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>56</v>
@@ -4492,7 +4492,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>56</v>
@@ -4530,7 +4530,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>56</v>
@@ -4568,7 +4568,7 @@
         <v>26</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>56</v>
@@ -4606,7 +4606,7 @@
         <v>26</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>56</v>
@@ -4644,7 +4644,7 @@
         <v>26</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>56</v>
@@ -4682,7 +4682,7 @@
         <v>108</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>56</v>
@@ -4720,7 +4720,7 @@
         <v>26</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>56</v>
@@ -4758,7 +4758,7 @@
         <v>26</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>56</v>
@@ -4796,7 +4796,7 @@
         <v>26</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>56</v>
@@ -4834,7 +4834,7 @@
         <v>26</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>56</v>
@@ -4872,7 +4872,7 @@
         <v>26</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>56</v>
@@ -4910,7 +4910,7 @@
         <v>26</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>56</v>
@@ -4948,7 +4948,7 @@
         <v>26</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>56</v>
@@ -4986,7 +4986,7 @@
         <v>15</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>56</v>
@@ -5024,7 +5024,7 @@
         <v>15</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>56</v>
@@ -5062,7 +5062,7 @@
         <v>26</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>56</v>
@@ -5100,7 +5100,7 @@
         <v>26</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>56</v>
@@ -5138,7 +5138,7 @@
         <v>17</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>56</v>
@@ -5176,7 +5176,7 @@
         <v>26</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>56</v>
@@ -5214,7 +5214,7 @@
         <v>26</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>56</v>
@@ -5252,7 +5252,7 @@
         <v>15</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>56</v>
@@ -5290,7 +5290,7 @@
         <v>26</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>56</v>
@@ -5328,7 +5328,7 @@
         <v>26</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>56</v>
@@ -5366,7 +5366,7 @@
         <v>26</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>56</v>
@@ -5404,7 +5404,7 @@
         <v>108</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>56</v>
@@ -5442,7 +5442,7 @@
         <v>26</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>56</v>
@@ -5480,7 +5480,7 @@
         <v>26</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>56</v>
@@ -5518,7 +5518,7 @@
         <v>26</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>56</v>
@@ -5556,7 +5556,7 @@
         <v>26</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>56</v>
@@ -5594,7 +5594,7 @@
         <v>15</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>56</v>
@@ -5632,7 +5632,7 @@
         <v>15</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>56</v>
@@ -5670,7 +5670,7 @@
         <v>26</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>56</v>
@@ -5708,7 +5708,7 @@
         <v>26</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>56</v>
@@ -5746,7 +5746,7 @@
         <v>26</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>56</v>
@@ -5784,7 +5784,7 @@
         <v>26</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>56</v>
@@ -5822,7 +5822,7 @@
         <v>26</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>56</v>
@@ -5860,7 +5860,7 @@
         <v>26</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>215</v>
@@ -5898,7 +5898,7 @@
         <v>26</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>215</v>
@@ -5936,7 +5936,7 @@
         <v>26</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>215</v>
@@ -5974,7 +5974,7 @@
         <v>26</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>215</v>
@@ -6012,7 +6012,7 @@
         <v>26</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>215</v>
@@ -6050,7 +6050,7 @@
         <v>26</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>215</v>
@@ -6088,7 +6088,7 @@
         <v>26</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>215</v>
@@ -6126,7 +6126,7 @@
         <v>26</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>215</v>
@@ -6164,7 +6164,7 @@
         <v>26</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>215</v>
@@ -6202,7 +6202,7 @@
         <v>26</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>215</v>
@@ -6240,7 +6240,7 @@
         <v>26</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>215</v>
@@ -6278,7 +6278,7 @@
         <v>26</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>215</v>
@@ -6316,7 +6316,7 @@
         <v>26</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>215</v>
@@ -6354,7 +6354,7 @@
         <v>26</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>215</v>
@@ -6392,7 +6392,7 @@
         <v>26</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>215</v>
@@ -6430,7 +6430,7 @@
         <v>108</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>215</v>
@@ -6468,7 +6468,7 @@
         <v>26</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>215</v>
@@ -6506,7 +6506,7 @@
         <v>26</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>215</v>
@@ -6544,7 +6544,7 @@
         <v>26</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>215</v>
@@ -6582,7 +6582,7 @@
         <v>26</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>215</v>
@@ -6620,7 +6620,7 @@
         <v>26</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>215</v>
@@ -6658,7 +6658,7 @@
         <v>26</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>215</v>
@@ -6696,7 +6696,7 @@
         <v>26</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>215</v>
@@ -6734,7 +6734,7 @@
         <v>26</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>215</v>
@@ -6772,7 +6772,7 @@
         <v>26</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>215</v>
@@ -6810,7 +6810,7 @@
         <v>26</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>215</v>
@@ -6848,7 +6848,7 @@
         <v>26</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>215</v>
@@ -6886,7 +6886,7 @@
         <v>26</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>215</v>
@@ -6924,7 +6924,7 @@
         <v>26</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>215</v>
@@ -6962,7 +6962,7 @@
         <v>26</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>215</v>
@@ -7000,7 +7000,7 @@
         <v>26</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>215</v>
@@ -7038,7 +7038,7 @@
         <v>26</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>215</v>
@@ -7076,7 +7076,7 @@
         <v>26</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>215</v>
@@ -7114,7 +7114,7 @@
         <v>26</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>215</v>
@@ -7152,7 +7152,7 @@
         <v>26</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>215</v>
@@ -7190,7 +7190,7 @@
         <v>26</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>215</v>
@@ -7228,7 +7228,7 @@
         <v>26</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>215</v>
@@ -7266,7 +7266,7 @@
         <v>26</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>215</v>
@@ -7304,7 +7304,7 @@
         <v>26</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>215</v>
@@ -7342,7 +7342,7 @@
         <v>26</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>215</v>
@@ -7380,7 +7380,7 @@
         <v>26</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>215</v>
@@ -7418,7 +7418,7 @@
         <v>26</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>215</v>
@@ -7456,7 +7456,7 @@
         <v>26</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>215</v>
@@ -7494,7 +7494,7 @@
         <v>26</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>215</v>
@@ -7532,7 +7532,7 @@
         <v>26</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>215</v>
@@ -7570,7 +7570,7 @@
         <v>16</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>368</v>
@@ -7608,7 +7608,7 @@
         <v>108</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>368</v>
@@ -7646,7 +7646,7 @@
         <v>26</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>368</v>
@@ -7684,7 +7684,7 @@
         <v>15</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>368</v>
@@ -7722,7 +7722,7 @@
         <v>26</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>368</v>
@@ -7760,7 +7760,7 @@
         <v>108</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>368</v>
@@ -7798,7 +7798,7 @@
         <v>108</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>368</v>
@@ -7836,7 +7836,7 @@
         <v>26</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>368</v>
@@ -7871,10 +7871,10 @@
         <v>397</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>983</v>
+        <v>1124</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>368</v>
@@ -7912,7 +7912,7 @@
         <v>26</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>368</v>
@@ -7950,7 +7950,7 @@
         <v>15</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>368</v>
@@ -7985,10 +7985,10 @@
         <v>408</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>86</v>
+        <v>26</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>986</v>
+        <v>1125</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>368</v>
@@ -8026,7 +8026,7 @@
         <v>108</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>368</v>
@@ -8064,7 +8064,7 @@
         <v>86</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>368</v>
@@ -8102,7 +8102,7 @@
         <v>26</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>368</v>
@@ -8140,7 +8140,7 @@
         <v>26</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>368</v>
@@ -8178,7 +8178,7 @@
         <v>108</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>368</v>
@@ -8216,7 +8216,7 @@
         <v>26</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>368</v>
@@ -8254,7 +8254,7 @@
         <v>15</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>368</v>
@@ -8292,7 +8292,7 @@
         <v>108</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>368</v>
@@ -8330,7 +8330,7 @@
         <v>26</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>368</v>
@@ -8368,7 +8368,7 @@
         <v>108</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>368</v>
@@ -8406,7 +8406,7 @@
         <v>108</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>368</v>
@@ -8444,7 +8444,7 @@
         <v>15</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>368</v>
@@ -8482,7 +8482,7 @@
         <v>15</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>368</v>
@@ -8520,7 +8520,7 @@
         <v>16</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>368</v>
@@ -8558,7 +8558,7 @@
         <v>16</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>368</v>
@@ -8596,7 +8596,7 @@
         <v>26</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>368</v>
@@ -8634,7 +8634,7 @@
         <v>26</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>368</v>
@@ -8672,7 +8672,7 @@
         <v>86</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>368</v>
@@ -8710,7 +8710,7 @@
         <v>108</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>368</v>
@@ -8748,7 +8748,7 @@
         <v>26</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>368</v>
@@ -8786,7 +8786,7 @@
         <v>15</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>368</v>
@@ -8824,7 +8824,7 @@
         <v>86</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>368</v>
@@ -8862,7 +8862,7 @@
         <v>16</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>368</v>
@@ -8900,7 +8900,7 @@
         <v>15</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>368</v>
@@ -8938,7 +8938,7 @@
         <v>26</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>368</v>
@@ -8976,7 +8976,7 @@
         <v>26</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>368</v>
@@ -9014,7 +9014,7 @@
         <v>26</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>368</v>
@@ -9052,7 +9052,7 @@
         <v>15</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>368</v>
@@ -9090,7 +9090,7 @@
         <v>26</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>368</v>
@@ -9128,7 +9128,7 @@
         <v>26</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>368</v>
@@ -9166,7 +9166,7 @@
         <v>26</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>368</v>
@@ -9204,7 +9204,7 @@
         <v>108</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>368</v>
@@ -9242,7 +9242,7 @@
         <v>15</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>368</v>
@@ -9280,7 +9280,7 @@
         <v>15</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>368</v>
@@ -9318,7 +9318,7 @@
         <v>26</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>368</v>
@@ -9356,7 +9356,7 @@
         <v>26</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>368</v>
@@ -9394,7 +9394,7 @@
         <v>108</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>368</v>
@@ -9432,7 +9432,7 @@
         <v>26</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>368</v>
@@ -9470,7 +9470,7 @@
         <v>31</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>549</v>
@@ -9508,7 +9508,7 @@
         <v>16</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>549</v>
@@ -9546,7 +9546,7 @@
         <v>31</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>549</v>
@@ -9584,7 +9584,7 @@
         <v>26</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>549</v>
@@ -9622,7 +9622,7 @@
         <v>15</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>549</v>
@@ -9660,7 +9660,7 @@
         <v>31</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>549</v>
@@ -9698,7 +9698,7 @@
         <v>26</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>549</v>
@@ -9736,7 +9736,7 @@
         <v>31</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>549</v>
@@ -9774,7 +9774,7 @@
         <v>26</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>549</v>
@@ -9812,7 +9812,7 @@
         <v>26</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>549</v>
@@ -9850,7 +9850,7 @@
         <v>108</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>549</v>
@@ -9888,7 +9888,7 @@
         <v>26</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>549</v>
@@ -9926,7 +9926,7 @@
         <v>26</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>549</v>
@@ -9964,7 +9964,7 @@
         <v>26</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>1038</v>
+        <v>1035</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>549</v>
@@ -10002,7 +10002,7 @@
         <v>26</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>549</v>
@@ -10040,7 +10040,7 @@
         <v>15</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>549</v>
@@ -10078,7 +10078,7 @@
         <v>15</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>549</v>
@@ -10116,7 +10116,7 @@
         <v>26</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>549</v>
@@ -10154,7 +10154,7 @@
         <v>26</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>549</v>
@@ -10192,7 +10192,7 @@
         <v>16</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>549</v>
@@ -10230,7 +10230,7 @@
         <v>16</v>
       </c>
       <c r="D171" s="5" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>549</v>
@@ -10268,7 +10268,7 @@
         <v>26</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>549</v>
@@ -10306,7 +10306,7 @@
         <v>26</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>549</v>
@@ -10344,7 +10344,7 @@
         <v>108</v>
       </c>
       <c r="D174" s="5" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>549</v>
@@ -10382,7 +10382,7 @@
         <v>26</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>549</v>
@@ -10420,7 +10420,7 @@
         <v>26</v>
       </c>
       <c r="D176" s="5" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>549</v>
@@ -10458,7 +10458,7 @@
         <v>31</v>
       </c>
       <c r="D177" s="5" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>549</v>
@@ -10496,7 +10496,7 @@
         <v>15</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>549</v>
@@ -10534,7 +10534,7 @@
         <v>108</v>
       </c>
       <c r="D179" s="5" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>549</v>
@@ -10572,7 +10572,7 @@
         <v>26</v>
       </c>
       <c r="D180" s="5" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>549</v>
@@ -10610,7 +10610,7 @@
         <v>31</v>
       </c>
       <c r="D181" s="5" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>549</v>
@@ -10648,7 +10648,7 @@
         <v>26</v>
       </c>
       <c r="D182" s="5" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>549</v>
@@ -10686,7 +10686,7 @@
         <v>26</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>549</v>
@@ -10724,7 +10724,7 @@
         <v>15</v>
       </c>
       <c r="D184" s="5" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="E184" s="1" t="s">
         <v>549</v>
@@ -10762,7 +10762,7 @@
         <v>15</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="E185" s="1" t="s">
         <v>549</v>
@@ -10800,7 +10800,7 @@
         <v>26</v>
       </c>
       <c r="D186" s="5" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>549</v>
@@ -10838,7 +10838,7 @@
         <v>15</v>
       </c>
       <c r="D187" s="5" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>549</v>
@@ -10876,7 +10876,7 @@
         <v>26</v>
       </c>
       <c r="D188" s="5" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>549</v>
@@ -10914,7 +10914,7 @@
         <v>16</v>
       </c>
       <c r="D189" s="5" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>549</v>
@@ -10952,7 +10952,7 @@
         <v>15</v>
       </c>
       <c r="D190" s="5" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="E190" s="1" t="s">
         <v>549</v>
@@ -10990,7 +10990,7 @@
         <v>16</v>
       </c>
       <c r="D191" s="5" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="E191" s="1" t="s">
         <v>667</v>
@@ -11028,7 +11028,7 @@
         <v>15</v>
       </c>
       <c r="D192" s="5" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>667</v>
@@ -11066,7 +11066,7 @@
         <v>16</v>
       </c>
       <c r="D193" s="5" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>667</v>
@@ -11104,7 +11104,7 @@
         <v>26</v>
       </c>
       <c r="D194" s="5" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="E194" s="1" t="s">
         <v>667</v>
@@ -11142,7 +11142,7 @@
         <v>682</v>
       </c>
       <c r="D195" s="5" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="E195" s="1" t="s">
         <v>667</v>
@@ -11180,7 +11180,7 @@
         <v>26</v>
       </c>
       <c r="D196" s="5" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="E196" s="1" t="s">
         <v>667</v>
@@ -11218,7 +11218,7 @@
         <v>26</v>
       </c>
       <c r="D197" s="5" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="E197" s="1" t="s">
         <v>667</v>
@@ -11256,7 +11256,7 @@
         <v>26</v>
       </c>
       <c r="D198" s="5" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="E198" s="1" t="s">
         <v>667</v>
@@ -11294,7 +11294,7 @@
         <v>26</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="E199" s="1" t="s">
         <v>667</v>
@@ -11332,7 +11332,7 @@
         <v>26</v>
       </c>
       <c r="D200" s="5" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="E200" s="1" t="s">
         <v>667</v>
@@ -11370,7 +11370,7 @@
         <v>15</v>
       </c>
       <c r="D201" s="5" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
       <c r="E201" s="1" t="s">
         <v>667</v>
@@ -11408,7 +11408,7 @@
         <v>26</v>
       </c>
       <c r="D202" s="5" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="E202" s="1" t="s">
         <v>667</v>
@@ -11446,7 +11446,7 @@
         <v>16</v>
       </c>
       <c r="D203" s="5" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
       <c r="E203" s="1" t="s">
         <v>667</v>
@@ -11484,7 +11484,7 @@
         <v>16</v>
       </c>
       <c r="D204" s="5" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>667</v>
@@ -11522,7 +11522,7 @@
         <v>26</v>
       </c>
       <c r="D205" s="5" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="E205" s="1" t="s">
         <v>667</v>
@@ -11560,7 +11560,7 @@
         <v>15</v>
       </c>
       <c r="D206" s="5" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="E206" s="1" t="s">
         <v>667</v>
@@ -11598,7 +11598,7 @@
         <v>15</v>
       </c>
       <c r="D207" s="5" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="E207" s="1" t="s">
         <v>667</v>
@@ -11636,7 +11636,7 @@
         <v>26</v>
       </c>
       <c r="D208" s="5" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="E208" s="1" t="s">
         <v>667</v>
@@ -11674,7 +11674,7 @@
         <v>26</v>
       </c>
       <c r="D209" s="5" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="E209" s="1" t="s">
         <v>667</v>
@@ -11712,7 +11712,7 @@
         <v>26</v>
       </c>
       <c r="D210" s="5" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="E210" s="1" t="s">
         <v>667</v>
@@ -11750,7 +11750,7 @@
         <v>26</v>
       </c>
       <c r="D211" s="5" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="E211" s="1" t="s">
         <v>667</v>
@@ -11788,7 +11788,7 @@
         <v>26</v>
       </c>
       <c r="D212" s="5" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="E212" s="1" t="s">
         <v>667</v>
@@ -11826,7 +11826,7 @@
         <v>16</v>
       </c>
       <c r="D213" s="5" t="s">
-        <v>1087</v>
+        <v>1084</v>
       </c>
       <c r="E213" s="1" t="s">
         <v>667</v>
@@ -11864,7 +11864,7 @@
         <v>15</v>
       </c>
       <c r="D214" s="5" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="E214" s="1" t="s">
         <v>667</v>
@@ -11902,7 +11902,7 @@
         <v>26</v>
       </c>
       <c r="D215" s="5" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
       <c r="E215" s="1" t="s">
         <v>667</v>
@@ -11940,7 +11940,7 @@
         <v>16</v>
       </c>
       <c r="D216" s="5" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="E216" s="1" t="s">
         <v>667</v>
@@ -11978,7 +11978,7 @@
         <v>26</v>
       </c>
       <c r="D217" s="5" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
       <c r="E217" s="1" t="s">
         <v>667</v>
@@ -12016,7 +12016,7 @@
         <v>682</v>
       </c>
       <c r="D218" s="5" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="E218" s="1" t="s">
         <v>667</v>
@@ -12054,7 +12054,7 @@
         <v>26</v>
       </c>
       <c r="D219" s="5" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
       <c r="E219" s="1" t="s">
         <v>667</v>
@@ -12092,7 +12092,7 @@
         <v>682</v>
       </c>
       <c r="D220" s="5" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>667</v>
@@ -12130,7 +12130,7 @@
         <v>26</v>
       </c>
       <c r="D221" s="5" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>667</v>
@@ -12168,7 +12168,7 @@
         <v>26</v>
       </c>
       <c r="D222" s="5" t="s">
-        <v>1096</v>
+        <v>1093</v>
       </c>
       <c r="E222" s="1" t="s">
         <v>667</v>
@@ -12206,7 +12206,7 @@
         <v>16</v>
       </c>
       <c r="D223" s="5" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="E223" s="1" t="s">
         <v>667</v>
@@ -12244,7 +12244,7 @@
         <v>26</v>
       </c>
       <c r="D224" s="5" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
       <c r="E224" s="1" t="s">
         <v>667</v>
@@ -12282,7 +12282,7 @@
         <v>26</v>
       </c>
       <c r="D225" s="5" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>667</v>
@@ -12320,7 +12320,7 @@
         <v>16</v>
       </c>
       <c r="D226" s="5" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="E226" s="1" t="s">
         <v>667</v>
@@ -12358,7 +12358,7 @@
         <v>26</v>
       </c>
       <c r="D227" s="5" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="E227" s="1" t="s">
         <v>667</v>
@@ -12396,7 +12396,7 @@
         <v>26</v>
       </c>
       <c r="D228" s="5" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="E228" s="1" t="s">
         <v>667</v>
@@ -12434,7 +12434,7 @@
         <v>26</v>
       </c>
       <c r="D229" s="5" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="E229" s="1" t="s">
         <v>667</v>
@@ -12472,7 +12472,7 @@
         <v>26</v>
       </c>
       <c r="D230" s="5" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="E230" s="1" t="s">
         <v>667</v>
@@ -12510,7 +12510,7 @@
         <v>31</v>
       </c>
       <c r="D231" s="5" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="E231" s="1" t="s">
         <v>549</v>
@@ -12548,7 +12548,7 @@
         <v>26</v>
       </c>
       <c r="D232" s="5" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
       <c r="E232" s="1" t="s">
         <v>667</v>
@@ -12586,7 +12586,7 @@
         <v>31</v>
       </c>
       <c r="D233" s="5" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="E233" s="1" t="s">
         <v>549</v>
@@ -12624,7 +12624,7 @@
         <v>108</v>
       </c>
       <c r="D234" s="5" t="s">
-        <v>1108</v>
+        <v>1105</v>
       </c>
       <c r="E234" s="1" t="s">
         <v>667</v>
@@ -12662,7 +12662,7 @@
         <v>15</v>
       </c>
       <c r="D235" s="5" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
       <c r="E235" s="1" t="s">
         <v>549</v>
@@ -12700,7 +12700,7 @@
         <v>26</v>
       </c>
       <c r="D236" s="5" t="s">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="E236" s="1" t="s">
         <v>667</v>
@@ -12738,7 +12738,7 @@
         <v>108</v>
       </c>
       <c r="D237" s="5" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="E237" s="1" t="s">
         <v>667</v>
@@ -12776,7 +12776,7 @@
         <v>26</v>
       </c>
       <c r="D238" s="5" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
       <c r="E238" s="1" t="s">
         <v>549</v>
@@ -12814,7 +12814,7 @@
         <v>26</v>
       </c>
       <c r="D239" s="5" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="E239" s="1" t="s">
         <v>549</v>
@@ -12852,7 +12852,7 @@
         <v>31</v>
       </c>
       <c r="D240" s="5" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="E240" s="1" t="s">
         <v>549</v>
@@ -12890,7 +12890,7 @@
         <v>15</v>
       </c>
       <c r="D241" s="5" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="E241" s="1" t="s">
         <v>549</v>
@@ -12928,7 +12928,7 @@
         <v>15</v>
       </c>
       <c r="D242" s="5" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
       <c r="E242" s="1" t="s">
         <v>667</v>
@@ -12966,7 +12966,7 @@
         <v>26</v>
       </c>
       <c r="D243" s="5" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="E243" s="1" t="s">
         <v>667</v>
@@ -13004,7 +13004,7 @@
         <v>26</v>
       </c>
       <c r="D244" s="5" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="E244" s="1" t="s">
         <v>667</v>
@@ -13042,7 +13042,7 @@
         <v>15</v>
       </c>
       <c r="D245" s="5" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
       <c r="E245" s="1" t="s">
         <v>667</v>
@@ -13080,7 +13080,7 @@
         <v>108</v>
       </c>
       <c r="D246" s="5" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="E246" s="1" t="s">
         <v>667</v>
@@ -13118,7 +13118,7 @@
         <v>108</v>
       </c>
       <c r="D247" s="5" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
       <c r="E247" s="1" t="s">
         <v>549</v>
@@ -13156,7 +13156,7 @@
         <v>26</v>
       </c>
       <c r="D248" s="5" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
       <c r="E248" s="1" t="s">
         <v>549</v>
@@ -13194,7 +13194,7 @@
         <v>26</v>
       </c>
       <c r="D249" s="5" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="E249" s="1" t="s">
         <v>667</v>
@@ -13232,7 +13232,7 @@
         <v>26</v>
       </c>
       <c r="D250" s="5" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
       <c r="E250" s="1" t="s">
         <v>667</v>
@@ -13270,7 +13270,7 @@
         <v>15</v>
       </c>
       <c r="D251" s="5" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
       <c r="E251" s="1" t="s">
         <v>667</v>
